--- a/artfynd/A 7214-2026 artfynd.xlsx
+++ b/artfynd/A 7214-2026 artfynd.xlsx
@@ -787,47 +787,47 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131334158</v>
+        <v>131334261</v>
       </c>
       <c r="B3" t="n">
-        <v>58057</v>
+        <v>99034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493840</v>
+        <v>493838</v>
       </c>
       <c r="R3" t="n">
-        <v>6676215</v>
+        <v>6676206</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,12 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Mellan äldre och yngre skog.</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1145,47 +1140,47 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131334261</v>
+        <v>131334158</v>
       </c>
       <c r="B6" t="n">
-        <v>99034</v>
+        <v>58057</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1194,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493838</v>
+        <v>493840</v>
       </c>
       <c r="R6" t="n">
-        <v>6676206</v>
+        <v>6676215</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1229,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1239,7 +1234,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Mellan äldre och yngre skog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2529,44 +2529,57 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131334595</v>
+        <v>131333773</v>
       </c>
       <c r="B18" t="n">
-        <v>91848</v>
+        <v>99034</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493840</v>
+        <v>493773</v>
       </c>
       <c r="R18" t="n">
-        <v>6676287</v>
+        <v>6676285</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2595,7 +2608,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2605,7 +2618,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ant. Flera det fanns snö kvar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2620,12 +2638,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2739,57 +2757,44 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131333773</v>
+        <v>131334595</v>
       </c>
       <c r="B20" t="n">
-        <v>99034</v>
+        <v>91848</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493773</v>
+        <v>493840</v>
       </c>
       <c r="R20" t="n">
-        <v>6676285</v>
+        <v>6676287</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2818,7 +2823,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2828,12 +2833,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ant. Flera det fanns snö kvar.</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2848,22 +2848,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131334166</v>
+        <v>131333621</v>
       </c>
       <c r="B21" t="n">
-        <v>92288</v>
+        <v>99034</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2871,37 +2871,51 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493800</v>
+        <v>493698</v>
       </c>
       <c r="R21" t="n">
-        <v>6676342</v>
+        <v>6676232</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2930,7 +2944,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2940,7 +2954,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2955,65 +2969,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131334199</v>
+        <v>131334166</v>
       </c>
       <c r="B22" t="n">
-        <v>57895</v>
+        <v>92288</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493835</v>
+        <v>493800</v>
       </c>
       <c r="R22" t="n">
-        <v>6676206</v>
+        <v>6676342</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3042,7 +3051,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3052,12 +3061,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Spillning på kanten, används troligen av någon.</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3072,59 +3076,50 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131333621</v>
+        <v>131334199</v>
       </c>
       <c r="B23" t="n">
-        <v>99034</v>
+        <v>57895</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3133,10 +3128,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493698</v>
+        <v>493835</v>
       </c>
       <c r="R23" t="n">
-        <v>6676232</v>
+        <v>6676206</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3168,7 +3163,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3178,7 +3173,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Spillning på kanten, används troligen av någon.</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 7214-2026 artfynd.xlsx
+++ b/artfynd/A 7214-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131334034</v>
+        <v>131334014</v>
       </c>
       <c r="B2" t="n">
-        <v>4773</v>
+        <v>93117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,27 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100299</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493833</v>
+        <v>493766</v>
       </c>
       <c r="R2" t="n">
-        <v>6676350</v>
+        <v>6676216</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,59 +779,54 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131334261</v>
+        <v>131334077</v>
       </c>
       <c r="B3" t="n">
-        <v>99034</v>
+        <v>93117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -836,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493838</v>
+        <v>493772</v>
       </c>
       <c r="R3" t="n">
-        <v>6676206</v>
+        <v>6676229</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131334014</v>
+        <v>131334034</v>
       </c>
       <c r="B4" t="n">
-        <v>93116</v>
+        <v>4774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,31 +918,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -952,13 +947,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493766</v>
+        <v>493833</v>
       </c>
       <c r="R4" t="n">
-        <v>6676216</v>
+        <v>6676350</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,54 +1007,59 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131334077</v>
+        <v>131334158</v>
       </c>
       <c r="B5" t="n">
-        <v>93116</v>
+        <v>58058</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1068,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493772</v>
+        <v>493840</v>
       </c>
       <c r="R5" t="n">
-        <v>6676229</v>
+        <v>6676215</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1113,7 +1113,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Mellan äldre och yngre skog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,47 +1145,47 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131334158</v>
+        <v>131334261</v>
       </c>
       <c r="B6" t="n">
-        <v>58057</v>
+        <v>99035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1189,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493840</v>
+        <v>493838</v>
       </c>
       <c r="R6" t="n">
-        <v>6676215</v>
+        <v>6676206</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1224,7 +1229,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,12 +1239,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Mellan äldre och yngre skog.</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,7 +1269,7 @@
         <v>131333871</v>
       </c>
       <c r="B7" t="n">
-        <v>97274</v>
+        <v>97275</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>131333748</v>
       </c>
       <c r="B8" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>131335349</v>
       </c>
       <c r="B9" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>131333681</v>
       </c>
       <c r="B10" t="n">
-        <v>97274</v>
+        <v>97275</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,38 +1699,47 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131334143</v>
+        <v>131333525</v>
       </c>
       <c r="B11" t="n">
-        <v>57898</v>
+        <v>99035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1739,13 +1748,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493853</v>
+        <v>493710</v>
       </c>
       <c r="R11" t="n">
-        <v>6676360</v>
+        <v>6676254</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1774,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1784,12 +1793,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre ringhack på Gran</t>
+          <t>Några överblommade, runt tallstam</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,62 +1813,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131334659</v>
+        <v>131335070</v>
       </c>
       <c r="B12" t="n">
-        <v>57077</v>
+        <v>92289</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493854</v>
+        <v>493806</v>
       </c>
       <c r="R12" t="n">
-        <v>6676295</v>
+        <v>6676345</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1891,7 +1898,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1901,20 +1908,16 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Trolig järpe, under gran.</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1926,58 +1929,60 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Karl Ericson, Bo karlstens, Erik Danielsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131335070</v>
+        <v>131334143</v>
       </c>
       <c r="B13" t="n">
-        <v>92288</v>
+        <v>57899</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493806</v>
+        <v>493853</v>
       </c>
       <c r="R13" t="n">
-        <v>6676345</v>
+        <v>6676360</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2006,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2016,7 +2021,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på Gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2025,29 +2035,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Karl Ericson, Bo karlstens, Erik Danielsson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131333525</v>
+        <v>131333559</v>
       </c>
       <c r="B14" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2079,7 +2088,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2093,7 +2102,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493710</v>
+        <v>493702</v>
       </c>
       <c r="R14" t="n">
         <v>6676254</v>
@@ -2128,7 +2137,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,12 +2147,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Några överblommade, runt tallstam</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,47 +2174,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131333559</v>
+        <v>131333951</v>
       </c>
       <c r="B15" t="n">
-        <v>99034</v>
+        <v>93117</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2219,10 +2218,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493702</v>
+        <v>493761</v>
       </c>
       <c r="R15" t="n">
-        <v>6676254</v>
+        <v>6676203</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2254,7 +2253,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2264,7 +2263,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Mest troligt dropp, kanske skarp.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,42 +2295,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131333951</v>
+        <v>131335314</v>
       </c>
       <c r="B16" t="n">
-        <v>93116</v>
+        <v>57899</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493761</v>
+        <v>493768</v>
       </c>
       <c r="R16" t="n">
-        <v>6676203</v>
+        <v>6676338</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2380,12 +2380,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Mest troligt dropp, kanske skarp.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2412,38 +2412,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131335314</v>
+        <v>131333773</v>
       </c>
       <c r="B17" t="n">
-        <v>57898</v>
+        <v>99035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2452,13 +2456,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493768</v>
+        <v>493773</v>
       </c>
       <c r="R17" t="n">
-        <v>6676338</v>
+        <v>6676285</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2487,7 +2491,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2497,12 +2501,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Ant. Flera det fanns snö kvar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2517,69 +2521,56 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131333773</v>
+        <v>131334595</v>
       </c>
       <c r="B18" t="n">
-        <v>99034</v>
+        <v>91849</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493773</v>
+        <v>493840</v>
       </c>
       <c r="R18" t="n">
-        <v>6676285</v>
+        <v>6676287</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2608,7 +2599,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2618,12 +2609,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ant. Flera det fanns snö kvar.</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2638,12 +2624,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2653,7 +2639,7 @@
         <v>131332689</v>
       </c>
       <c r="B19" t="n">
-        <v>92288</v>
+        <v>92289</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2757,41 +2743,59 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131334595</v>
+        <v>131333621</v>
       </c>
       <c r="B20" t="n">
-        <v>91848</v>
+        <v>99035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493840</v>
+        <v>493698</v>
       </c>
       <c r="R20" t="n">
-        <v>6676287</v>
+        <v>6676232</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2823,7 +2827,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2833,7 +2837,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2860,10 +2864,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131333621</v>
+        <v>131334166</v>
       </c>
       <c r="B21" t="n">
-        <v>99034</v>
+        <v>92289</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2871,51 +2875,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493698</v>
+        <v>493800</v>
       </c>
       <c r="R21" t="n">
-        <v>6676232</v>
+        <v>6676342</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2944,7 +2934,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2954,7 +2944,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2969,60 +2959,65 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131334166</v>
+        <v>131334199</v>
       </c>
       <c r="B22" t="n">
-        <v>92288</v>
+        <v>57896</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493800</v>
+        <v>493835</v>
       </c>
       <c r="R22" t="n">
-        <v>6676342</v>
+        <v>6676206</v>
       </c>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3051,7 +3046,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3061,7 +3056,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Spillning på kanten, används troligen av någon.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3076,50 +3076,50 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131334199</v>
+        <v>131333841</v>
       </c>
       <c r="B23" t="n">
-        <v>57895</v>
+        <v>99035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3128,10 +3128,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>493835</v>
+        <v>493757</v>
       </c>
       <c r="R23" t="n">
-        <v>6676206</v>
+        <v>6676208</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3173,12 +3173,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Spillning på kanten, används troligen av någon.</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3202,118 +3197,6 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>131333841</v>
-      </c>
-      <c r="B24" t="n">
-        <v>99034</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Sexberget, Sexberget, Dlr</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>493757</v>
-      </c>
-      <c r="R24" t="n">
-        <v>6676208</v>
-      </c>
-      <c r="S24" t="n">
-        <v>5</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Ludvika</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Grangärde</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>12:39</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>12:39</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Karl Ericson</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Karl Ericson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7214-2026 artfynd.xlsx
+++ b/artfynd/A 7214-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131334014</v>
       </c>
       <c r="B2" t="n">
-        <v>93117</v>
+        <v>93120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>131334077</v>
       </c>
       <c r="B3" t="n">
-        <v>93117</v>
+        <v>93120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>131334158</v>
       </c>
       <c r="B5" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>131334261</v>
       </c>
       <c r="B6" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>131333871</v>
       </c>
       <c r="B7" t="n">
-        <v>97275</v>
+        <v>97278</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>131333748</v>
       </c>
       <c r="B8" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>131335349</v>
       </c>
       <c r="B9" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>131333681</v>
       </c>
       <c r="B10" t="n">
-        <v>97275</v>
+        <v>97278</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>131333525</v>
       </c>
       <c r="B11" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>131335070</v>
       </c>
       <c r="B12" t="n">
-        <v>92289</v>
+        <v>92292</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Karl Ericson, Bo karlstens, Erik Danielsson</t>
+          <t>Karl Ericson, Erik Danielsson, Bo karlstens</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1939,7 +1939,7 @@
         <v>131334143</v>
       </c>
       <c r="B13" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>131333559</v>
       </c>
       <c r="B14" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>131333951</v>
       </c>
       <c r="B15" t="n">
-        <v>93117</v>
+        <v>93120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>131335314</v>
       </c>
       <c r="B16" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131333773</v>
+        <v>131332689</v>
       </c>
       <c r="B17" t="n">
-        <v>99035</v>
+        <v>92292</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,46 +2423,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493773</v>
+        <v>493701</v>
       </c>
       <c r="R17" t="n">
-        <v>6676285</v>
+        <v>6676314</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2491,7 +2482,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2501,12 +2492,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ant. Flera det fanns snö kvar.</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2521,12 +2507,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2536,7 +2522,7 @@
         <v>131334595</v>
       </c>
       <c r="B18" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2636,10 +2622,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131332689</v>
+        <v>131333773</v>
       </c>
       <c r="B19" t="n">
-        <v>92289</v>
+        <v>99038</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2647,37 +2633,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493701</v>
+        <v>493773</v>
       </c>
       <c r="R19" t="n">
-        <v>6676314</v>
+        <v>6676285</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2706,7 +2701,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2716,7 +2711,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ant. Flera det fanns snö kvar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2731,22 +2731,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131333621</v>
+        <v>131334166</v>
       </c>
       <c r="B20" t="n">
-        <v>99035</v>
+        <v>92292</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2754,51 +2754,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493698</v>
+        <v>493800</v>
       </c>
       <c r="R20" t="n">
-        <v>6676232</v>
+        <v>6676342</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2827,7 +2813,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2837,7 +2823,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2852,22 +2838,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131334166</v>
+        <v>131333621</v>
       </c>
       <c r="B21" t="n">
-        <v>92289</v>
+        <v>99038</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2875,37 +2861,51 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493800</v>
+        <v>493698</v>
       </c>
       <c r="R21" t="n">
-        <v>6676342</v>
+        <v>6676232</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2959,12 +2959,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2974,7 +2974,7 @@
         <v>131334199</v>
       </c>
       <c r="B22" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>131333841</v>
       </c>
       <c r="B23" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 7214-2026 artfynd.xlsx
+++ b/artfynd/A 7214-2026 artfynd.xlsx
@@ -675,42 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131334014</v>
+        <v>131334158</v>
       </c>
       <c r="B2" t="n">
-        <v>93120</v>
+        <v>58061</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493766</v>
+        <v>493840</v>
       </c>
       <c r="R2" t="n">
-        <v>6676216</v>
+        <v>6676215</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Mellan äldre och yngre skog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131334077</v>
+        <v>131334014</v>
       </c>
       <c r="B3" t="n">
         <v>93120</v>
@@ -835,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493772</v>
+        <v>493766</v>
       </c>
       <c r="R3" t="n">
-        <v>6676229</v>
+        <v>6676216</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131334034</v>
+        <v>131334077</v>
       </c>
       <c r="B4" t="n">
-        <v>4774</v>
+        <v>93120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,27 +928,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100299</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -947,13 +961,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493833</v>
+        <v>493772</v>
       </c>
       <c r="R4" t="n">
-        <v>6676350</v>
+        <v>6676229</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,7 +996,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +1006,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,59 +1021,50 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131334158</v>
+        <v>131334034</v>
       </c>
       <c r="B5" t="n">
-        <v>58061</v>
+        <v>4774</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1068,13 +1073,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493840</v>
+        <v>493833</v>
       </c>
       <c r="R5" t="n">
-        <v>6676215</v>
+        <v>6676350</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,7 +1108,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1113,12 +1118,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Mellan äldre och yngre skog.</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,12 +1133,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1699,47 +1699,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131333525</v>
+        <v>131334143</v>
       </c>
       <c r="B11" t="n">
-        <v>99038</v>
+        <v>57902</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1748,13 +1739,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493710</v>
+        <v>493853</v>
       </c>
       <c r="R11" t="n">
-        <v>6676254</v>
+        <v>6676360</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1783,7 +1774,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,12 +1784,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Några överblommade, runt tallstam</t>
+          <t>Äldre ringhack på Gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,22 +1804,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131335070</v>
+        <v>131333525</v>
       </c>
       <c r="B12" t="n">
-        <v>92292</v>
+        <v>99038</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1836,37 +1827,48 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493806</v>
+        <v>493710</v>
       </c>
       <c r="R12" t="n">
-        <v>6676345</v>
+        <v>6676254</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1898,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1908,7 +1910,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Några överblommade, runt tallstam</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,7 +1924,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1929,60 +1935,58 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Karl Ericson, Erik Danielsson, Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131334143</v>
+        <v>131335070</v>
       </c>
       <c r="B13" t="n">
-        <v>57902</v>
+        <v>92292</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493853</v>
+        <v>493806</v>
       </c>
       <c r="R13" t="n">
-        <v>6676360</v>
+        <v>6676345</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2011,7 +2015,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,12 +2025,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på Gran</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2035,18 +2034,19 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson, Bo karlstens, Erik Danielsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 7214-2026 artfynd.xlsx
+++ b/artfynd/A 7214-2026 artfynd.xlsx
@@ -675,47 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131334158</v>
+        <v>131334014</v>
       </c>
       <c r="B2" t="n">
-        <v>58061</v>
+        <v>93120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493840</v>
+        <v>493766</v>
       </c>
       <c r="R2" t="n">
-        <v>6676215</v>
+        <v>6676216</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Mellan äldre och yngre skog.</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131334014</v>
+        <v>131334077</v>
       </c>
       <c r="B3" t="n">
         <v>93120</v>
@@ -845,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493766</v>
+        <v>493772</v>
       </c>
       <c r="R3" t="n">
-        <v>6676216</v>
+        <v>6676229</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -880,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131334077</v>
+        <v>131334034</v>
       </c>
       <c r="B4" t="n">
-        <v>93120</v>
+        <v>4774</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,31 +918,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -961,13 +947,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493772</v>
+        <v>493833</v>
       </c>
       <c r="R4" t="n">
-        <v>6676229</v>
+        <v>6676350</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1006,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,50 +1007,59 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131334034</v>
+        <v>131334158</v>
       </c>
       <c r="B5" t="n">
-        <v>4774</v>
+        <v>58061</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1073,13 +1068,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493833</v>
+        <v>493840</v>
       </c>
       <c r="R5" t="n">
-        <v>6676350</v>
+        <v>6676215</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,7 +1103,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1118,7 +1113,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Mellan äldre och yngre skog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,12 +1133,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -2412,34 +2412,30 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131332689</v>
+        <v>131334595</v>
       </c>
       <c r="B17" t="n">
-        <v>92292</v>
+        <v>91852</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2447,13 +2443,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493701</v>
+        <v>493840</v>
       </c>
       <c r="R17" t="n">
-        <v>6676314</v>
+        <v>6676287</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2482,7 +2478,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2492,7 +2488,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2507,42 +2503,46 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131334595</v>
+        <v>131332689</v>
       </c>
       <c r="B18" t="n">
-        <v>91852</v>
+        <v>92292</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2550,13 +2550,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493840</v>
+        <v>493701</v>
       </c>
       <c r="R18" t="n">
-        <v>6676287</v>
+        <v>6676314</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2610,12 +2610,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2850,47 +2850,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131333621</v>
+        <v>131334199</v>
       </c>
       <c r="B21" t="n">
-        <v>99038</v>
+        <v>57899</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2899,10 +2890,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493698</v>
+        <v>493835</v>
       </c>
       <c r="R21" t="n">
-        <v>6676232</v>
+        <v>6676206</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2934,7 +2925,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2944,7 +2935,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Spillning på kanten, används troligen av någon.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2971,38 +2967,47 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131334199</v>
+        <v>131333621</v>
       </c>
       <c r="B22" t="n">
-        <v>57899</v>
+        <v>99038</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3011,10 +3016,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493835</v>
+        <v>493698</v>
       </c>
       <c r="R22" t="n">
-        <v>6676206</v>
+        <v>6676232</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3046,7 +3051,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3056,12 +3061,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Spillning på kanten, används troligen av någon.</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 7214-2026 artfynd.xlsx
+++ b/artfynd/A 7214-2026 artfynd.xlsx
@@ -675,42 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131334014</v>
+        <v>131334158</v>
       </c>
       <c r="B2" t="n">
-        <v>93120</v>
+        <v>58063</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493766</v>
+        <v>493840</v>
       </c>
       <c r="R2" t="n">
-        <v>6676216</v>
+        <v>6676215</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Mellan äldre och yngre skog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,42 +801,47 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131334077</v>
+        <v>131334261</v>
       </c>
       <c r="B3" t="n">
-        <v>93120</v>
+        <v>99044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493772</v>
+        <v>493838</v>
       </c>
       <c r="R3" t="n">
-        <v>6676229</v>
+        <v>6676206</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +895,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1019,47 +1034,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131334158</v>
+        <v>131334014</v>
       </c>
       <c r="B5" t="n">
-        <v>58061</v>
+        <v>93126</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1068,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493840</v>
+        <v>493766</v>
       </c>
       <c r="R5" t="n">
-        <v>6676215</v>
+        <v>6676216</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1113,12 +1123,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Mellan äldre och yngre skog.</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,47 +1150,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131334261</v>
+        <v>131334077</v>
       </c>
       <c r="B6" t="n">
-        <v>99038</v>
+        <v>93126</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493838</v>
+        <v>493772</v>
       </c>
       <c r="R6" t="n">
-        <v>6676206</v>
+        <v>6676229</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,7 +1269,7 @@
         <v>131333871</v>
       </c>
       <c r="B7" t="n">
-        <v>97278</v>
+        <v>97284</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>131333748</v>
       </c>
       <c r="B8" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>131335349</v>
       </c>
       <c r="B9" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>131333681</v>
       </c>
       <c r="B10" t="n">
-        <v>97278</v>
+        <v>97284</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,38 +1699,47 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131334143</v>
+        <v>131333525</v>
       </c>
       <c r="B11" t="n">
-        <v>57902</v>
+        <v>99044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1739,13 +1748,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493853</v>
+        <v>493710</v>
       </c>
       <c r="R11" t="n">
-        <v>6676360</v>
+        <v>6676254</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1774,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1784,12 +1793,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre ringhack på Gran</t>
+          <t>Några överblommade, runt tallstam</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,22 +1813,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131333525</v>
+        <v>131335070</v>
       </c>
       <c r="B12" t="n">
-        <v>99038</v>
+        <v>92298</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1827,48 +1836,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493710</v>
+        <v>493806</v>
       </c>
       <c r="R12" t="n">
-        <v>6676254</v>
+        <v>6676345</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1900,7 +1898,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,12 +1908,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Några överblommade, runt tallstam</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1924,6 +1917,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1935,58 +1929,60 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Karl Ericson, Bo karlstens, Erik Danielsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131335070</v>
+        <v>131334143</v>
       </c>
       <c r="B13" t="n">
-        <v>92292</v>
+        <v>57904</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493806</v>
+        <v>493853</v>
       </c>
       <c r="R13" t="n">
-        <v>6676345</v>
+        <v>6676360</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2015,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2025,7 +2021,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på Gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2034,19 +2035,18 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Karl Ericson, Bo karlstens, Erik Danielsson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2056,7 +2056,7 @@
         <v>131333559</v>
       </c>
       <c r="B14" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>131333951</v>
       </c>
       <c r="B15" t="n">
-        <v>93120</v>
+        <v>93126</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>131335314</v>
       </c>
       <c r="B16" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2412,44 +2412,57 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131334595</v>
+        <v>131333773</v>
       </c>
       <c r="B17" t="n">
-        <v>91852</v>
+        <v>99044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493840</v>
+        <v>493773</v>
       </c>
       <c r="R17" t="n">
-        <v>6676287</v>
+        <v>6676285</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2478,7 +2491,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2488,7 +2501,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ant. Flera det fanns snö kvar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2503,12 +2521,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2518,7 +2536,7 @@
         <v>131332689</v>
       </c>
       <c r="B18" t="n">
-        <v>92292</v>
+        <v>92298</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2622,57 +2640,44 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131333773</v>
+        <v>131334595</v>
       </c>
       <c r="B19" t="n">
-        <v>99038</v>
+        <v>91858</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493773</v>
+        <v>493840</v>
       </c>
       <c r="R19" t="n">
-        <v>6676285</v>
+        <v>6676287</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2701,7 +2706,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2711,12 +2716,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ant. Flera det fanns snö kvar.</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2731,22 +2731,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131334166</v>
+        <v>131333621</v>
       </c>
       <c r="B20" t="n">
-        <v>92292</v>
+        <v>99044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2754,37 +2754,51 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493800</v>
+        <v>493698</v>
       </c>
       <c r="R20" t="n">
-        <v>6676342</v>
+        <v>6676232</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2813,7 +2827,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2823,7 +2837,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2838,65 +2852,60 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131334199</v>
+        <v>131334166</v>
       </c>
       <c r="B21" t="n">
-        <v>57899</v>
+        <v>92298</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493835</v>
+        <v>493800</v>
       </c>
       <c r="R21" t="n">
-        <v>6676206</v>
+        <v>6676342</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2925,7 +2934,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2935,12 +2944,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Spillning på kanten, används troligen av någon.</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2955,59 +2959,50 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131333621</v>
+        <v>131334199</v>
       </c>
       <c r="B22" t="n">
-        <v>99038</v>
+        <v>57901</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3016,10 +3011,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493698</v>
+        <v>493835</v>
       </c>
       <c r="R22" t="n">
-        <v>6676232</v>
+        <v>6676206</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3051,7 +3046,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3061,7 +3056,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Spillning på kanten, används troligen av någon.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3091,7 +3091,7 @@
         <v>131333841</v>
       </c>
       <c r="B23" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 7214-2026 artfynd.xlsx
+++ b/artfynd/A 7214-2026 artfynd.xlsx
@@ -2743,47 +2743,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131333621</v>
+        <v>131334199</v>
       </c>
       <c r="B20" t="n">
-        <v>99044</v>
+        <v>57901</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2792,10 +2783,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493698</v>
+        <v>493835</v>
       </c>
       <c r="R20" t="n">
-        <v>6676232</v>
+        <v>6676206</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2827,7 +2818,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2837,7 +2828,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Spillning på kanten, används troligen av någon.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2864,10 +2860,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131334166</v>
+        <v>131333621</v>
       </c>
       <c r="B21" t="n">
-        <v>92298</v>
+        <v>99044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2875,37 +2871,51 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493800</v>
+        <v>493698</v>
       </c>
       <c r="R21" t="n">
-        <v>6676342</v>
+        <v>6676232</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2934,7 +2944,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2944,7 +2954,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2959,65 +2969,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131334199</v>
+        <v>131334166</v>
       </c>
       <c r="B22" t="n">
-        <v>57901</v>
+        <v>92298</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493835</v>
+        <v>493800</v>
       </c>
       <c r="R22" t="n">
-        <v>6676206</v>
+        <v>6676342</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3046,7 +3051,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3056,12 +3061,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Spillning på kanten, används troligen av någon.</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3076,12 +3076,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 7214-2026 artfynd.xlsx
+++ b/artfynd/A 7214-2026 artfynd.xlsx
@@ -1699,47 +1699,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131333525</v>
+        <v>131334143</v>
       </c>
       <c r="B11" t="n">
-        <v>99044</v>
+        <v>57904</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1748,13 +1739,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493710</v>
+        <v>493853</v>
       </c>
       <c r="R11" t="n">
-        <v>6676254</v>
+        <v>6676360</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1783,7 +1774,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,12 +1784,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Några överblommade, runt tallstam</t>
+          <t>Äldre ringhack på Gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,12 +1804,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1936,38 +1927,47 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131334143</v>
+        <v>131333525</v>
       </c>
       <c r="B13" t="n">
-        <v>57904</v>
+        <v>99044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493853</v>
+        <v>493710</v>
       </c>
       <c r="R13" t="n">
-        <v>6676360</v>
+        <v>6676254</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,12 +2021,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack på Gran</t>
+          <t>Några överblommade, runt tallstam</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,12 +2041,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131333773</v>
+        <v>131332689</v>
       </c>
       <c r="B17" t="n">
-        <v>99044</v>
+        <v>92298</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,46 +2423,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493773</v>
+        <v>493701</v>
       </c>
       <c r="R17" t="n">
-        <v>6676285</v>
+        <v>6676314</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2491,7 +2482,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2501,12 +2492,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ant. Flera det fanns snö kvar.</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2521,46 +2507,42 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131332689</v>
+        <v>131334595</v>
       </c>
       <c r="B18" t="n">
-        <v>92298</v>
+        <v>91858</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2568,13 +2550,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493701</v>
+        <v>493840</v>
       </c>
       <c r="R18" t="n">
-        <v>6676314</v>
+        <v>6676287</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2603,7 +2585,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2613,7 +2595,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,56 +2610,69 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131334595</v>
+        <v>131333773</v>
       </c>
       <c r="B19" t="n">
-        <v>91858</v>
+        <v>99044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493840</v>
+        <v>493773</v>
       </c>
       <c r="R19" t="n">
-        <v>6676287</v>
+        <v>6676285</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2706,7 +2701,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2716,7 +2711,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ant. Flera det fanns snö kvar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2731,12 +2731,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 7214-2026 artfynd.xlsx
+++ b/artfynd/A 7214-2026 artfynd.xlsx
@@ -1699,38 +1699,47 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131334143</v>
+        <v>131333525</v>
       </c>
       <c r="B11" t="n">
-        <v>57904</v>
+        <v>99044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1739,13 +1748,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493853</v>
+        <v>493710</v>
       </c>
       <c r="R11" t="n">
-        <v>6676360</v>
+        <v>6676254</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1774,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1784,12 +1793,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre ringhack på Gran</t>
+          <t>Några överblommade, runt tallstam</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,12 +1813,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1927,47 +1936,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131333525</v>
+        <v>131334143</v>
       </c>
       <c r="B13" t="n">
-        <v>99044</v>
+        <v>57904</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493710</v>
+        <v>493853</v>
       </c>
       <c r="R13" t="n">
-        <v>6676254</v>
+        <v>6676360</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,12 +2021,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Några överblommade, runt tallstam</t>
+          <t>Äldre ringhack på Gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,12 +2041,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131332689</v>
+        <v>131333773</v>
       </c>
       <c r="B17" t="n">
-        <v>92298</v>
+        <v>99044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,37 +2423,46 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493701</v>
+        <v>493773</v>
       </c>
       <c r="R17" t="n">
-        <v>6676314</v>
+        <v>6676285</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2482,7 +2491,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2492,7 +2501,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ant. Flera det fanns snö kvar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2507,42 +2521,46 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131334595</v>
+        <v>131332689</v>
       </c>
       <c r="B18" t="n">
-        <v>91858</v>
+        <v>92298</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2550,13 +2568,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493840</v>
+        <v>493701</v>
       </c>
       <c r="R18" t="n">
-        <v>6676287</v>
+        <v>6676314</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2585,7 +2603,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2595,7 +2613,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2610,69 +2628,56 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131333773</v>
+        <v>131334595</v>
       </c>
       <c r="B19" t="n">
-        <v>99044</v>
+        <v>91858</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493773</v>
+        <v>493840</v>
       </c>
       <c r="R19" t="n">
-        <v>6676285</v>
+        <v>6676287</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2701,7 +2706,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2711,12 +2716,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ant. Flera det fanns snö kvar.</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2731,12 +2731,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 7214-2026 artfynd.xlsx
+++ b/artfynd/A 7214-2026 artfynd.xlsx
@@ -675,47 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131334158</v>
+        <v>131334261</v>
       </c>
       <c r="B2" t="n">
-        <v>58063</v>
+        <v>99047</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493840</v>
+        <v>493838</v>
       </c>
       <c r="R2" t="n">
-        <v>6676215</v>
+        <v>6676206</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Mellan äldre och yngre skog.</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,47 +796,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131334261</v>
+        <v>131334014</v>
       </c>
       <c r="B3" t="n">
-        <v>99044</v>
+        <v>93129</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -850,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493838</v>
+        <v>493766</v>
       </c>
       <c r="R3" t="n">
-        <v>6676206</v>
+        <v>6676216</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -885,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131334034</v>
+        <v>131334077</v>
       </c>
       <c r="B4" t="n">
-        <v>4774</v>
+        <v>93129</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,27 +923,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100299</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -962,13 +956,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493833</v>
+        <v>493772</v>
       </c>
       <c r="R4" t="n">
-        <v>6676350</v>
+        <v>6676229</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +1001,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,22 +1016,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131334014</v>
+        <v>131334034</v>
       </c>
       <c r="B5" t="n">
-        <v>93126</v>
+        <v>4775</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1045,31 +1039,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>100299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1078,13 +1068,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493766</v>
+        <v>493833</v>
       </c>
       <c r="R5" t="n">
-        <v>6676216</v>
+        <v>6676350</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,7 +1103,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1113,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,54 +1128,59 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131334077</v>
+        <v>131334158</v>
       </c>
       <c r="B6" t="n">
-        <v>93126</v>
+        <v>58066</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1194,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493772</v>
+        <v>493840</v>
       </c>
       <c r="R6" t="n">
-        <v>6676229</v>
+        <v>6676215</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1229,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1239,7 +1234,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Mellan äldre och yngre skog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,7 +1269,7 @@
         <v>131333871</v>
       </c>
       <c r="B7" t="n">
-        <v>97284</v>
+        <v>97287</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>131333748</v>
       </c>
       <c r="B8" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>131335349</v>
       </c>
       <c r="B9" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>131333681</v>
       </c>
       <c r="B10" t="n">
-        <v>97284</v>
+        <v>97287</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131333525</v>
+        <v>131335070</v>
       </c>
       <c r="B11" t="n">
-        <v>99044</v>
+        <v>92301</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1710,48 +1710,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493710</v>
+        <v>493806</v>
       </c>
       <c r="R11" t="n">
-        <v>6676254</v>
+        <v>6676345</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1783,7 +1772,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,12 +1782,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Några överblommade, runt tallstam</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1807,6 +1791,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1818,58 +1803,60 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Karl Ericson, Bo karlstens, Erik Danielsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131335070</v>
+        <v>131334143</v>
       </c>
       <c r="B12" t="n">
-        <v>92298</v>
+        <v>57907</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493806</v>
+        <v>493853</v>
       </c>
       <c r="R12" t="n">
-        <v>6676345</v>
+        <v>6676360</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1898,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1908,7 +1895,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på Gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,57 +1909,65 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Karl Ericson, Bo karlstens, Erik Danielsson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131334143</v>
+        <v>131333525</v>
       </c>
       <c r="B13" t="n">
-        <v>57904</v>
+        <v>99047</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493853</v>
+        <v>493710</v>
       </c>
       <c r="R13" t="n">
-        <v>6676360</v>
+        <v>6676254</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,12 +2021,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack på Gran</t>
+          <t>Några överblommade, runt tallstam</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,12 +2041,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2056,7 +2056,7 @@
         <v>131333559</v>
       </c>
       <c r="B14" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>131333951</v>
       </c>
       <c r="B15" t="n">
-        <v>93126</v>
+        <v>93129</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>131335314</v>
       </c>
       <c r="B16" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>131333773</v>
       </c>
       <c r="B17" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2533,34 +2533,30 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131332689</v>
+        <v>131334595</v>
       </c>
       <c r="B18" t="n">
-        <v>92298</v>
+        <v>91861</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2568,13 +2564,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493701</v>
+        <v>493840</v>
       </c>
       <c r="R18" t="n">
-        <v>6676314</v>
+        <v>6676287</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2603,7 +2599,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2613,7 +2609,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,42 +2624,46 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131334595</v>
+        <v>131332689</v>
       </c>
       <c r="B19" t="n">
-        <v>91858</v>
+        <v>92301</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2671,13 +2671,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493840</v>
+        <v>493701</v>
       </c>
       <c r="R19" t="n">
-        <v>6676287</v>
+        <v>6676314</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2731,12 +2731,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2746,7 +2746,7 @@
         <v>131334199</v>
       </c>
       <c r="B20" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
         <v>131333621</v>
       </c>
       <c r="B21" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>131334166</v>
       </c>
       <c r="B22" t="n">
-        <v>92298</v>
+        <v>92301</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>131333841</v>
       </c>
       <c r="B23" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 7214-2026 artfynd.xlsx
+++ b/artfynd/A 7214-2026 artfynd.xlsx
@@ -675,47 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131334261</v>
+        <v>131334014</v>
       </c>
       <c r="B2" t="n">
-        <v>99047</v>
+        <v>93134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493838</v>
+        <v>493766</v>
       </c>
       <c r="R2" t="n">
-        <v>6676206</v>
+        <v>6676216</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131334014</v>
+        <v>131334077</v>
       </c>
       <c r="B3" t="n">
-        <v>93129</v>
+        <v>93134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493766</v>
+        <v>493772</v>
       </c>
       <c r="R3" t="n">
-        <v>6676216</v>
+        <v>6676229</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -875,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,42 +907,47 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131334077</v>
+        <v>131334158</v>
       </c>
       <c r="B4" t="n">
-        <v>93129</v>
+        <v>58071</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -956,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493772</v>
+        <v>493840</v>
       </c>
       <c r="R4" t="n">
-        <v>6676229</v>
+        <v>6676215</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -991,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,7 +1001,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mellan äldre och yngre skog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1140,47 +1145,47 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131334158</v>
+        <v>131334261</v>
       </c>
       <c r="B6" t="n">
-        <v>58066</v>
+        <v>99052</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1189,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493840</v>
+        <v>493838</v>
       </c>
       <c r="R6" t="n">
-        <v>6676215</v>
+        <v>6676206</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1224,7 +1229,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,12 +1239,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Mellan äldre och yngre skog.</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,7 +1269,7 @@
         <v>131333871</v>
       </c>
       <c r="B7" t="n">
-        <v>97287</v>
+        <v>97292</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>131333748</v>
       </c>
       <c r="B8" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>131335349</v>
       </c>
       <c r="B9" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>131333681</v>
       </c>
       <c r="B10" t="n">
-        <v>97287</v>
+        <v>97292</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131335070</v>
+        <v>131333525</v>
       </c>
       <c r="B11" t="n">
-        <v>92301</v>
+        <v>99052</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1710,37 +1710,48 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493806</v>
+        <v>493710</v>
       </c>
       <c r="R11" t="n">
-        <v>6676345</v>
+        <v>6676254</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1772,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1782,7 +1793,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Några överblommade, runt tallstam</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1791,7 +1807,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1803,7 +1818,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Karl Ericson, Bo karlstens, Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1813,7 +1828,7 @@
         <v>131334143</v>
       </c>
       <c r="B12" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,10 +1942,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131333525</v>
+        <v>131335070</v>
       </c>
       <c r="B13" t="n">
-        <v>99047</v>
+        <v>92306</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1938,48 +1953,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493710</v>
+        <v>493806</v>
       </c>
       <c r="R13" t="n">
-        <v>6676254</v>
+        <v>6676345</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2011,7 +2015,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,12 +2025,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Några överblommade, runt tallstam</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2035,6 +2034,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Karl Ericson, Bo karlstens, Erik Danielsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2056,7 +2056,7 @@
         <v>131333559</v>
       </c>
       <c r="B14" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>131333951</v>
       </c>
       <c r="B15" t="n">
-        <v>93129</v>
+        <v>93134</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>131335314</v>
       </c>
       <c r="B16" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>131333773</v>
       </c>
       <c r="B17" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>131334595</v>
       </c>
       <c r="B18" t="n">
-        <v>91861</v>
+        <v>91866</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>131332689</v>
       </c>
       <c r="B19" t="n">
-        <v>92301</v>
+        <v>92306</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2743,38 +2743,47 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131334199</v>
+        <v>131333621</v>
       </c>
       <c r="B20" t="n">
-        <v>57904</v>
+        <v>99052</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2783,10 +2792,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493835</v>
+        <v>493698</v>
       </c>
       <c r="R20" t="n">
-        <v>6676206</v>
+        <v>6676232</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2818,7 +2827,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2828,12 +2837,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Spillning på kanten, används troligen av någon.</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2860,47 +2864,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131333621</v>
+        <v>131334199</v>
       </c>
       <c r="B21" t="n">
-        <v>99047</v>
+        <v>57909</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2909,10 +2904,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493698</v>
+        <v>493835</v>
       </c>
       <c r="R21" t="n">
-        <v>6676232</v>
+        <v>6676206</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2944,7 +2939,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2954,7 +2949,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Spillning på kanten, används troligen av någon.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2984,7 +2984,7 @@
         <v>131334166</v>
       </c>
       <c r="B22" t="n">
-        <v>92301</v>
+        <v>92306</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>131333841</v>
       </c>
       <c r="B23" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 7214-2026 artfynd.xlsx
+++ b/artfynd/A 7214-2026 artfynd.xlsx
@@ -1699,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131333525</v>
+        <v>131335070</v>
       </c>
       <c r="B11" t="n">
-        <v>99052</v>
+        <v>92306</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1710,48 +1710,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493710</v>
+        <v>493806</v>
       </c>
       <c r="R11" t="n">
-        <v>6676254</v>
+        <v>6676345</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1783,7 +1772,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,12 +1782,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Några överblommade, runt tallstam</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1807,6 +1791,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1818,45 +1803,54 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Karl Ericson, Bo karlstens, Erik Danielsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131334143</v>
+        <v>131333525</v>
       </c>
       <c r="B12" t="n">
-        <v>57912</v>
+        <v>99052</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1865,13 +1859,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493853</v>
+        <v>493710</v>
       </c>
       <c r="R12" t="n">
-        <v>6676360</v>
+        <v>6676254</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1900,7 +1894,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,12 +1904,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Äldre ringhack på Gran</t>
+          <t>Några överblommade, runt tallstam</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1930,63 +1924,65 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131335070</v>
+        <v>131334143</v>
       </c>
       <c r="B13" t="n">
-        <v>92306</v>
+        <v>57912</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493806</v>
+        <v>493853</v>
       </c>
       <c r="R13" t="n">
-        <v>6676345</v>
+        <v>6676360</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2015,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2025,7 +2021,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på Gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2034,19 +2035,18 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Karl Ericson, Bo karlstens, Erik Danielsson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131333773</v>
+        <v>131332689</v>
       </c>
       <c r="B17" t="n">
-        <v>99052</v>
+        <v>92306</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2423,46 +2423,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493773</v>
+        <v>493701</v>
       </c>
       <c r="R17" t="n">
-        <v>6676285</v>
+        <v>6676314</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2491,7 +2482,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2501,12 +2492,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ant. Flera det fanns snö kvar.</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2521,12 +2507,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2636,10 +2622,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131332689</v>
+        <v>131333773</v>
       </c>
       <c r="B19" t="n">
-        <v>92306</v>
+        <v>99052</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2647,37 +2633,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493701</v>
+        <v>493773</v>
       </c>
       <c r="R19" t="n">
-        <v>6676314</v>
+        <v>6676285</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2706,7 +2701,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2716,7 +2711,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ant. Flera det fanns snö kvar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2731,22 +2731,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131333621</v>
+        <v>131334166</v>
       </c>
       <c r="B20" t="n">
-        <v>99052</v>
+        <v>92306</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2754,51 +2754,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493698</v>
+        <v>493800</v>
       </c>
       <c r="R20" t="n">
-        <v>6676232</v>
+        <v>6676342</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2827,7 +2813,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2837,7 +2823,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2852,12 +2838,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2981,10 +2967,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131334166</v>
+        <v>131333621</v>
       </c>
       <c r="B22" t="n">
-        <v>92306</v>
+        <v>99052</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2992,37 +2978,51 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493800</v>
+        <v>493698</v>
       </c>
       <c r="R22" t="n">
-        <v>6676342</v>
+        <v>6676232</v>
       </c>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3076,12 +3076,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 7214-2026 artfynd.xlsx
+++ b/artfynd/A 7214-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131334014</v>
       </c>
       <c r="B2" t="n">
-        <v>93134</v>
+        <v>93136</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>131334077</v>
       </c>
       <c r="B3" t="n">
-        <v>93134</v>
+        <v>93136</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,47 +907,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131334158</v>
+        <v>131334034</v>
       </c>
       <c r="B4" t="n">
-        <v>58071</v>
+        <v>4775</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -956,13 +947,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493840</v>
+        <v>493833</v>
       </c>
       <c r="R4" t="n">
-        <v>6676215</v>
+        <v>6676350</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,12 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Mellan äldre och yngre skog.</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,50 +1007,59 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131334034</v>
+        <v>131334261</v>
       </c>
       <c r="B5" t="n">
-        <v>4775</v>
+        <v>99054</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1073,13 +1068,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493833</v>
+        <v>493838</v>
       </c>
       <c r="R5" t="n">
-        <v>6676350</v>
+        <v>6676206</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,7 +1103,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1118,7 +1113,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,59 +1128,59 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131334261</v>
+        <v>131334158</v>
       </c>
       <c r="B6" t="n">
-        <v>99052</v>
+        <v>58073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1194,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493838</v>
+        <v>493840</v>
       </c>
       <c r="R6" t="n">
-        <v>6676206</v>
+        <v>6676215</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1229,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1239,7 +1234,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Mellan äldre och yngre skog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,7 +1269,7 @@
         <v>131333871</v>
       </c>
       <c r="B7" t="n">
-        <v>97292</v>
+        <v>97294</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>131333748</v>
       </c>
       <c r="B8" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>131335349</v>
       </c>
       <c r="B9" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>131333681</v>
       </c>
       <c r="B10" t="n">
-        <v>97292</v>
+        <v>97294</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,51 +1699,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131335070</v>
+        <v>131334143</v>
       </c>
       <c r="B11" t="n">
-        <v>92306</v>
+        <v>57914</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493806</v>
+        <v>493853</v>
       </c>
       <c r="R11" t="n">
-        <v>6676345</v>
+        <v>6676360</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1772,7 +1774,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1782,7 +1784,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på Gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1791,29 +1798,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Karl Ericson, Bo karlstens, Erik Danielsson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131333525</v>
+        <v>131335070</v>
       </c>
       <c r="B12" t="n">
-        <v>99052</v>
+        <v>92308</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,48 +1827,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493710</v>
+        <v>493806</v>
       </c>
       <c r="R12" t="n">
-        <v>6676254</v>
+        <v>6676345</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1894,7 +1889,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1904,12 +1899,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Några överblommade, runt tallstam</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1918,6 +1908,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1929,45 +1920,54 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Karl Ericson, Erik Danielsson, Bo karlstens</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131334143</v>
+        <v>131333525</v>
       </c>
       <c r="B13" t="n">
-        <v>57912</v>
+        <v>99054</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493853</v>
+        <v>493710</v>
       </c>
       <c r="R13" t="n">
-        <v>6676360</v>
+        <v>6676254</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,12 +2021,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack på Gran</t>
+          <t>Några överblommade, runt tallstam</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,12 +2041,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2056,7 +2056,7 @@
         <v>131333559</v>
       </c>
       <c r="B14" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>131333951</v>
       </c>
       <c r="B15" t="n">
-        <v>93134</v>
+        <v>93136</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>131335314</v>
       </c>
       <c r="B16" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2412,34 +2412,30 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131332689</v>
+        <v>131334595</v>
       </c>
       <c r="B17" t="n">
-        <v>92306</v>
+        <v>91868</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2447,13 +2443,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493701</v>
+        <v>493840</v>
       </c>
       <c r="R17" t="n">
-        <v>6676314</v>
+        <v>6676287</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2482,7 +2478,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2492,7 +2488,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2507,42 +2503,46 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131334595</v>
+        <v>131332689</v>
       </c>
       <c r="B18" t="n">
-        <v>91866</v>
+        <v>92308</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2550,13 +2550,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493840</v>
+        <v>493701</v>
       </c>
       <c r="R18" t="n">
-        <v>6676287</v>
+        <v>6676314</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2610,12 +2610,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2625,7 +2625,7 @@
         <v>131333773</v>
       </c>
       <c r="B19" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2743,10 +2743,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131334166</v>
+        <v>131333621</v>
       </c>
       <c r="B20" t="n">
-        <v>92306</v>
+        <v>99054</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2754,37 +2754,51 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493800</v>
+        <v>493698</v>
       </c>
       <c r="R20" t="n">
-        <v>6676342</v>
+        <v>6676232</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2813,7 +2827,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2823,7 +2837,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2838,65 +2852,60 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131334199</v>
+        <v>131334166</v>
       </c>
       <c r="B21" t="n">
-        <v>57909</v>
+        <v>92308</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493835</v>
+        <v>493800</v>
       </c>
       <c r="R21" t="n">
-        <v>6676206</v>
+        <v>6676342</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2925,7 +2934,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2935,12 +2944,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Spillning på kanten, används troligen av någon.</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2955,59 +2959,50 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131333621</v>
+        <v>131334199</v>
       </c>
       <c r="B22" t="n">
-        <v>99052</v>
+        <v>57911</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3016,10 +3011,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493698</v>
+        <v>493835</v>
       </c>
       <c r="R22" t="n">
-        <v>6676232</v>
+        <v>6676206</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3051,7 +3046,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3061,7 +3056,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Spillning på kanten, används troligen av någon.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3091,7 +3091,7 @@
         <v>131333841</v>
       </c>
       <c r="B23" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 7214-2026 artfynd.xlsx
+++ b/artfynd/A 7214-2026 artfynd.xlsx
@@ -675,42 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131334014</v>
+        <v>131334158</v>
       </c>
       <c r="B2" t="n">
-        <v>93136</v>
+        <v>58073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493766</v>
+        <v>493840</v>
       </c>
       <c r="R2" t="n">
-        <v>6676216</v>
+        <v>6676215</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Mellan äldre och yngre skog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131334077</v>
+        <v>131334014</v>
       </c>
       <c r="B3" t="n">
         <v>93136</v>
@@ -835,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493772</v>
+        <v>493766</v>
       </c>
       <c r="R3" t="n">
-        <v>6676229</v>
+        <v>6676216</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131334034</v>
+        <v>131334077</v>
       </c>
       <c r="B4" t="n">
-        <v>4775</v>
+        <v>93136</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,27 +928,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100299</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -947,13 +961,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493833</v>
+        <v>493772</v>
       </c>
       <c r="R4" t="n">
-        <v>6676350</v>
+        <v>6676229</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,7 +996,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +1006,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,59 +1021,50 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131334261</v>
+        <v>131334034</v>
       </c>
       <c r="B5" t="n">
-        <v>99054</v>
+        <v>4775</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1068,13 +1073,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493838</v>
+        <v>493833</v>
       </c>
       <c r="R5" t="n">
-        <v>6676206</v>
+        <v>6676350</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,7 +1108,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1113,7 +1118,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,59 +1133,59 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131334158</v>
+        <v>131334261</v>
       </c>
       <c r="B6" t="n">
-        <v>58073</v>
+        <v>99054</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1189,10 +1194,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493840</v>
+        <v>493838</v>
       </c>
       <c r="R6" t="n">
-        <v>6676215</v>
+        <v>6676206</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1224,7 +1229,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,12 +1239,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Mellan äldre och yngre skog.</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 7214-2026 artfynd.xlsx
+++ b/artfynd/A 7214-2026 artfynd.xlsx
@@ -675,47 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131334158</v>
+        <v>131334014</v>
       </c>
       <c r="B2" t="n">
-        <v>58073</v>
+        <v>93136</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493840</v>
+        <v>493766</v>
       </c>
       <c r="R2" t="n">
-        <v>6676215</v>
+        <v>6676216</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Mellan äldre och yngre skog.</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131334014</v>
+        <v>131334077</v>
       </c>
       <c r="B3" t="n">
         <v>93136</v>
@@ -845,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493766</v>
+        <v>493772</v>
       </c>
       <c r="R3" t="n">
-        <v>6676216</v>
+        <v>6676229</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -880,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,42 +907,47 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131334077</v>
+        <v>131334261</v>
       </c>
       <c r="B4" t="n">
-        <v>93136</v>
+        <v>99054</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -961,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493772</v>
+        <v>493838</v>
       </c>
       <c r="R4" t="n">
-        <v>6676229</v>
+        <v>6676206</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -996,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1006,7 +1001,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1145,47 +1140,47 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131334261</v>
+        <v>131334158</v>
       </c>
       <c r="B6" t="n">
-        <v>99054</v>
+        <v>58073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1194,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493838</v>
+        <v>493840</v>
       </c>
       <c r="R6" t="n">
-        <v>6676206</v>
+        <v>6676215</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1229,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1239,7 +1234,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Mellan äldre och yngre skog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Karl Ericson, Erik Danielsson, Bo karlstens</t>
+          <t>Karl Ericson, Bo karlstens, Erik Danielsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2412,30 +2412,34 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131334595</v>
+        <v>131332689</v>
       </c>
       <c r="B17" t="n">
-        <v>91868</v>
+        <v>92308</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2443,13 +2447,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493840</v>
+        <v>493701</v>
       </c>
       <c r="R17" t="n">
-        <v>6676287</v>
+        <v>6676314</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2478,7 +2482,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2488,7 +2492,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2503,46 +2507,42 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131332689</v>
+        <v>131334595</v>
       </c>
       <c r="B18" t="n">
-        <v>92308</v>
+        <v>91868</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2550,13 +2550,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493701</v>
+        <v>493840</v>
       </c>
       <c r="R18" t="n">
-        <v>6676314</v>
+        <v>6676287</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2610,12 +2610,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2743,10 +2743,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131333621</v>
+        <v>131334166</v>
       </c>
       <c r="B20" t="n">
-        <v>99054</v>
+        <v>92308</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2754,51 +2754,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493698</v>
+        <v>493800</v>
       </c>
       <c r="R20" t="n">
-        <v>6676232</v>
+        <v>6676342</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2827,7 +2813,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2837,7 +2823,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2852,60 +2838,65 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131334166</v>
+        <v>131334199</v>
       </c>
       <c r="B21" t="n">
-        <v>92308</v>
+        <v>57911</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493800</v>
+        <v>493835</v>
       </c>
       <c r="R21" t="n">
-        <v>6676342</v>
+        <v>6676206</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2934,7 +2925,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2944,7 +2935,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Spillning på kanten, används troligen av någon.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2959,50 +2955,59 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131334199</v>
+        <v>131333621</v>
       </c>
       <c r="B22" t="n">
-        <v>57911</v>
+        <v>99054</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3011,10 +3016,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493835</v>
+        <v>493698</v>
       </c>
       <c r="R22" t="n">
-        <v>6676206</v>
+        <v>6676232</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3046,7 +3051,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3056,12 +3061,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Spillning på kanten, används troligen av någon.</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 7214-2026 artfynd.xlsx
+++ b/artfynd/A 7214-2026 artfynd.xlsx
@@ -675,42 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131334014</v>
+        <v>131334158</v>
       </c>
       <c r="B2" t="n">
-        <v>93136</v>
+        <v>58073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493766</v>
+        <v>493840</v>
       </c>
       <c r="R2" t="n">
-        <v>6676216</v>
+        <v>6676215</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Mellan äldre och yngre skog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,42 +801,47 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131334077</v>
+        <v>131334261</v>
       </c>
       <c r="B3" t="n">
-        <v>93136</v>
+        <v>99054</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493772</v>
+        <v>493838</v>
       </c>
       <c r="R3" t="n">
-        <v>6676229</v>
+        <v>6676206</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +895,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,47 +922,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131334261</v>
+        <v>131334014</v>
       </c>
       <c r="B4" t="n">
-        <v>99054</v>
+        <v>93136</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -956,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493838</v>
+        <v>493766</v>
       </c>
       <c r="R4" t="n">
-        <v>6676206</v>
+        <v>6676216</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -991,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131334034</v>
+        <v>131334077</v>
       </c>
       <c r="B5" t="n">
-        <v>4775</v>
+        <v>93136</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,27 +1049,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1068,13 +1082,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493833</v>
+        <v>493772</v>
       </c>
       <c r="R5" t="n">
-        <v>6676350</v>
+        <v>6676229</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,7 +1117,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1113,7 +1127,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,59 +1142,50 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131334158</v>
+        <v>131334034</v>
       </c>
       <c r="B6" t="n">
-        <v>58073</v>
+        <v>4775</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1189,13 +1194,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493840</v>
+        <v>493833</v>
       </c>
       <c r="R6" t="n">
-        <v>6676215</v>
+        <v>6676350</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,7 +1229,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,12 +1239,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Mellan äldre och yngre skog.</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,12 +1254,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1699,38 +1699,47 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131334143</v>
+        <v>131333525</v>
       </c>
       <c r="B11" t="n">
-        <v>57914</v>
+        <v>99054</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1739,13 +1748,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493853</v>
+        <v>493710</v>
       </c>
       <c r="R11" t="n">
-        <v>6676360</v>
+        <v>6676254</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1774,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1784,12 +1793,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre ringhack på Gran</t>
+          <t>Några överblommade, runt tallstam</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,12 +1813,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1927,47 +1936,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131333525</v>
+        <v>131334143</v>
       </c>
       <c r="B13" t="n">
-        <v>99054</v>
+        <v>57914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493710</v>
+        <v>493853</v>
       </c>
       <c r="R13" t="n">
-        <v>6676254</v>
+        <v>6676360</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,12 +2021,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Några överblommade, runt tallstam</t>
+          <t>Äldre ringhack på Gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,12 +2041,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2412,34 +2412,30 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131332689</v>
+        <v>131334595</v>
       </c>
       <c r="B17" t="n">
-        <v>92308</v>
+        <v>91868</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2447,13 +2443,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493701</v>
+        <v>493840</v>
       </c>
       <c r="R17" t="n">
-        <v>6676314</v>
+        <v>6676287</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2482,7 +2478,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2492,7 +2488,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2507,42 +2503,46 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131334595</v>
+        <v>131332689</v>
       </c>
       <c r="B18" t="n">
-        <v>91868</v>
+        <v>92308</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2550,13 +2550,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493840</v>
+        <v>493701</v>
       </c>
       <c r="R18" t="n">
-        <v>6676287</v>
+        <v>6676314</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2610,12 +2610,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 7214-2026 artfynd.xlsx
+++ b/artfynd/A 7214-2026 artfynd.xlsx
@@ -2412,44 +2412,57 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131334595</v>
+        <v>131333773</v>
       </c>
       <c r="B17" t="n">
-        <v>91868</v>
+        <v>99054</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493840</v>
+        <v>493773</v>
       </c>
       <c r="R17" t="n">
-        <v>6676287</v>
+        <v>6676285</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2478,7 +2491,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2488,7 +2501,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ant. Flera det fanns snö kvar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2503,46 +2521,42 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131332689</v>
+        <v>131334595</v>
       </c>
       <c r="B18" t="n">
-        <v>92308</v>
+        <v>91868</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2550,13 +2564,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493701</v>
+        <v>493840</v>
       </c>
       <c r="R18" t="n">
-        <v>6676314</v>
+        <v>6676287</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2585,7 +2599,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2595,7 +2609,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2610,22 +2624,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131333773</v>
+        <v>131332689</v>
       </c>
       <c r="B19" t="n">
-        <v>99054</v>
+        <v>92308</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2633,46 +2647,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493773</v>
+        <v>493701</v>
       </c>
       <c r="R19" t="n">
-        <v>6676285</v>
+        <v>6676314</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2701,7 +2706,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2711,12 +2716,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ant. Flera det fanns snö kvar.</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2731,12 +2731,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 7214-2026 artfynd.xlsx
+++ b/artfynd/A 7214-2026 artfynd.xlsx
@@ -675,47 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131334158</v>
+        <v>131334034</v>
       </c>
       <c r="B2" t="n">
-        <v>58073</v>
+        <v>4775</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493840</v>
+        <v>493833</v>
       </c>
       <c r="R2" t="n">
-        <v>6676215</v>
+        <v>6676350</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Mellan äldre och yngre skog.</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,59 +775,54 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131334261</v>
+        <v>131334014</v>
       </c>
       <c r="B3" t="n">
-        <v>99054</v>
+        <v>93136</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -850,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493838</v>
+        <v>493766</v>
       </c>
       <c r="R3" t="n">
-        <v>6676206</v>
+        <v>6676216</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -885,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131334014</v>
+        <v>131334077</v>
       </c>
       <c r="B4" t="n">
         <v>93136</v>
@@ -966,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493766</v>
+        <v>493772</v>
       </c>
       <c r="R4" t="n">
-        <v>6676216</v>
+        <v>6676229</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1001,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,42 +1019,47 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131334077</v>
+        <v>131334158</v>
       </c>
       <c r="B5" t="n">
-        <v>93136</v>
+        <v>58073</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1082,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493772</v>
+        <v>493840</v>
       </c>
       <c r="R5" t="n">
-        <v>6676229</v>
+        <v>6676215</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1117,7 +1103,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1127,7 +1113,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Mellan äldre och yngre skog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,38 +1145,47 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131334034</v>
+        <v>131334261</v>
       </c>
       <c r="B6" t="n">
-        <v>4775</v>
+        <v>99054</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493833</v>
+        <v>493838</v>
       </c>
       <c r="R6" t="n">
-        <v>6676350</v>
+        <v>6676206</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,12 +1254,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131333525</v>
+        <v>131335070</v>
       </c>
       <c r="B11" t="n">
-        <v>99054</v>
+        <v>92308</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1710,48 +1710,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493710</v>
+        <v>493806</v>
       </c>
       <c r="R11" t="n">
-        <v>6676254</v>
+        <v>6676345</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1783,7 +1772,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,12 +1782,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Några överblommade, runt tallstam</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1807,6 +1791,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1818,58 +1803,60 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Karl Ericson, Bo karlstens, Erik Danielsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131335070</v>
+        <v>131334143</v>
       </c>
       <c r="B12" t="n">
-        <v>92308</v>
+        <v>57914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493806</v>
+        <v>493853</v>
       </c>
       <c r="R12" t="n">
-        <v>6676345</v>
+        <v>6676360</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1898,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1908,7 +1895,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på Gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,57 +1909,65 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Karl Ericson, Bo karlstens, Erik Danielsson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131334143</v>
+        <v>131333525</v>
       </c>
       <c r="B13" t="n">
-        <v>57914</v>
+        <v>99054</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493853</v>
+        <v>493710</v>
       </c>
       <c r="R13" t="n">
-        <v>6676360</v>
+        <v>6676254</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,12 +2021,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack på Gran</t>
+          <t>Några överblommade, runt tallstam</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,12 +2041,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 7214-2026 artfynd.xlsx
+++ b/artfynd/A 7214-2026 artfynd.xlsx
@@ -675,38 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131334034</v>
+        <v>131334158</v>
       </c>
       <c r="B2" t="n">
-        <v>4775</v>
+        <v>58073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100299</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493833</v>
+        <v>493840</v>
       </c>
       <c r="R2" t="n">
-        <v>6676350</v>
+        <v>6676215</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Mellan äldre och yngre skog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,54 +789,59 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131334014</v>
+        <v>131334261</v>
       </c>
       <c r="B3" t="n">
-        <v>93136</v>
+        <v>99054</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493766</v>
+        <v>493838</v>
       </c>
       <c r="R3" t="n">
-        <v>6676216</v>
+        <v>6676206</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +895,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,7 +922,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131334077</v>
+        <v>131334014</v>
       </c>
       <c r="B4" t="n">
         <v>93136</v>
@@ -947,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493772</v>
+        <v>493766</v>
       </c>
       <c r="R4" t="n">
-        <v>6676229</v>
+        <v>6676216</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,47 +1038,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131334158</v>
+        <v>131334077</v>
       </c>
       <c r="B5" t="n">
-        <v>58073</v>
+        <v>93136</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1068,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493840</v>
+        <v>493772</v>
       </c>
       <c r="R5" t="n">
-        <v>6676215</v>
+        <v>6676229</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,7 +1117,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1113,12 +1127,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Mellan äldre och yngre skog.</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,47 +1154,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131334261</v>
+        <v>131334034</v>
       </c>
       <c r="B6" t="n">
-        <v>99054</v>
+        <v>4775</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493838</v>
+        <v>493833</v>
       </c>
       <c r="R6" t="n">
-        <v>6676206</v>
+        <v>6676350</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,12 +1254,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1810,38 +1810,47 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131334143</v>
+        <v>131333525</v>
       </c>
       <c r="B12" t="n">
-        <v>57914</v>
+        <v>99054</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1850,13 +1859,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493853</v>
+        <v>493710</v>
       </c>
       <c r="R12" t="n">
-        <v>6676360</v>
+        <v>6676254</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1885,7 +1894,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,12 +1904,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Äldre ringhack på Gran</t>
+          <t>Några överblommade, runt tallstam</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1915,59 +1924,50 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131333525</v>
+        <v>131334143</v>
       </c>
       <c r="B13" t="n">
-        <v>99054</v>
+        <v>57914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493710</v>
+        <v>493853</v>
       </c>
       <c r="R13" t="n">
-        <v>6676254</v>
+        <v>6676360</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,12 +2021,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Några överblommade, runt tallstam</t>
+          <t>Äldre ringhack på Gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,12 +2041,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2412,57 +2412,44 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131333773</v>
+        <v>131334595</v>
       </c>
       <c r="B17" t="n">
-        <v>99054</v>
+        <v>91868</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493773</v>
+        <v>493840</v>
       </c>
       <c r="R17" t="n">
-        <v>6676285</v>
+        <v>6676287</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2491,7 +2478,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2501,12 +2488,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ant. Flera det fanns snö kvar.</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2521,42 +2503,46 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131334595</v>
+        <v>131332689</v>
       </c>
       <c r="B18" t="n">
-        <v>91868</v>
+        <v>92308</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2564,13 +2550,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493840</v>
+        <v>493701</v>
       </c>
       <c r="R18" t="n">
-        <v>6676287</v>
+        <v>6676314</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2599,7 +2585,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2609,7 +2595,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2624,22 +2610,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131332689</v>
+        <v>131333773</v>
       </c>
       <c r="B19" t="n">
-        <v>92308</v>
+        <v>99054</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2647,37 +2633,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493701</v>
+        <v>493773</v>
       </c>
       <c r="R19" t="n">
-        <v>6676314</v>
+        <v>6676285</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2706,7 +2701,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2716,7 +2711,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ant. Flera det fanns snö kvar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2731,12 +2731,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 7214-2026 artfynd.xlsx
+++ b/artfynd/A 7214-2026 artfynd.xlsx
@@ -675,47 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131334158</v>
+        <v>131334014</v>
       </c>
       <c r="B2" t="n">
-        <v>58073</v>
+        <v>93172</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493840</v>
+        <v>493766</v>
       </c>
       <c r="R2" t="n">
-        <v>6676215</v>
+        <v>6676216</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Mellan äldre och yngre skog.</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,47 +791,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131334261</v>
+        <v>131334077</v>
       </c>
       <c r="B3" t="n">
-        <v>99054</v>
+        <v>93172</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -850,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493838</v>
+        <v>493772</v>
       </c>
       <c r="R3" t="n">
-        <v>6676206</v>
+        <v>6676229</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -885,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,42 +907,47 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131334014</v>
+        <v>131334158</v>
       </c>
       <c r="B4" t="n">
-        <v>93136</v>
+        <v>58107</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -966,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493766</v>
+        <v>493840</v>
       </c>
       <c r="R4" t="n">
-        <v>6676216</v>
+        <v>6676215</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1001,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1001,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mellan äldre och yngre skog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,42 +1033,47 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131334077</v>
+        <v>131334261</v>
       </c>
       <c r="B5" t="n">
-        <v>93136</v>
+        <v>99090</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1082,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493772</v>
+        <v>493838</v>
       </c>
       <c r="R5" t="n">
-        <v>6676229</v>
+        <v>6676206</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1269,7 +1269,7 @@
         <v>131333871</v>
       </c>
       <c r="B7" t="n">
-        <v>97294</v>
+        <v>97330</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>131333748</v>
       </c>
       <c r="B8" t="n">
-        <v>99054</v>
+        <v>99090</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>131335349</v>
       </c>
       <c r="B9" t="n">
-        <v>57911</v>
+        <v>57945</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>131333681</v>
       </c>
       <c r="B10" t="n">
-        <v>97294</v>
+        <v>97330</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,10 +1699,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131335070</v>
+        <v>131333525</v>
       </c>
       <c r="B11" t="n">
-        <v>92308</v>
+        <v>99090</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1710,37 +1710,48 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493806</v>
+        <v>493710</v>
       </c>
       <c r="R11" t="n">
-        <v>6676345</v>
+        <v>6676254</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1772,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1782,7 +1793,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Några överblommade, runt tallstam</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1791,7 +1807,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1803,17 +1818,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Karl Ericson, Bo karlstens, Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131333525</v>
+        <v>131335070</v>
       </c>
       <c r="B12" t="n">
-        <v>99054</v>
+        <v>92344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,48 +1836,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493710</v>
+        <v>493806</v>
       </c>
       <c r="R12" t="n">
-        <v>6676254</v>
+        <v>6676345</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1894,7 +1898,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1904,12 +1908,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Några överblommade, runt tallstam</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1918,6 +1917,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Karl Ericson, Bo karlstens, Erik Danielsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1939,7 +1939,7 @@
         <v>131334143</v>
       </c>
       <c r="B13" t="n">
-        <v>57914</v>
+        <v>57948</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>131333559</v>
       </c>
       <c r="B14" t="n">
-        <v>99054</v>
+        <v>99090</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>131333951</v>
       </c>
       <c r="B15" t="n">
-        <v>93136</v>
+        <v>93172</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>131335314</v>
       </c>
       <c r="B16" t="n">
-        <v>57914</v>
+        <v>57948</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2412,44 +2412,57 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131334595</v>
+        <v>131333773</v>
       </c>
       <c r="B17" t="n">
-        <v>91868</v>
+        <v>99090</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493840</v>
+        <v>493773</v>
       </c>
       <c r="R17" t="n">
-        <v>6676287</v>
+        <v>6676285</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2478,7 +2491,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2488,7 +2501,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ant. Flera det fanns snö kvar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2503,12 +2521,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2518,7 +2536,7 @@
         <v>131332689</v>
       </c>
       <c r="B18" t="n">
-        <v>92308</v>
+        <v>92344</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2622,57 +2640,44 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131333773</v>
+        <v>131334595</v>
       </c>
       <c r="B19" t="n">
-        <v>99054</v>
+        <v>91904</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493773</v>
+        <v>493840</v>
       </c>
       <c r="R19" t="n">
-        <v>6676285</v>
+        <v>6676287</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2701,7 +2706,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2711,12 +2716,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ant. Flera det fanns snö kvar.</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2731,12 +2731,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2746,7 +2746,7 @@
         <v>131334166</v>
       </c>
       <c r="B20" t="n">
-        <v>92308</v>
+        <v>92344</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         <v>131334199</v>
       </c>
       <c r="B21" t="n">
-        <v>57911</v>
+        <v>57945</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         <v>131333621</v>
       </c>
       <c r="B22" t="n">
-        <v>99054</v>
+        <v>99090</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
         <v>131333841</v>
       </c>
       <c r="B23" t="n">
-        <v>99054</v>
+        <v>99090</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 7214-2026 artfynd.xlsx
+++ b/artfynd/A 7214-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131334014</v>
       </c>
       <c r="B2" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>131334077</v>
       </c>
       <c r="B3" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,38 +907,47 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131334034</v>
+        <v>131334261</v>
       </c>
       <c r="B4" t="n">
-        <v>4775</v>
+        <v>99098</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -947,13 +956,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493833</v>
+        <v>493838</v>
       </c>
       <c r="R4" t="n">
-        <v>6676350</v>
+        <v>6676206</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +1001,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,12 +1016,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1022,7 +1031,7 @@
         <v>131334158</v>
       </c>
       <c r="B5" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,47 +1154,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131334261</v>
+        <v>131334034</v>
       </c>
       <c r="B6" t="n">
-        <v>99095</v>
+        <v>4775</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493838</v>
+        <v>493833</v>
       </c>
       <c r="R6" t="n">
-        <v>6676206</v>
+        <v>6676350</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,12 +1254,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1269,7 +1269,7 @@
         <v>131333871</v>
       </c>
       <c r="B7" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
         <v>131333748</v>
       </c>
       <c r="B8" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>131333681</v>
       </c>
       <c r="B10" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,51 +1699,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131335070</v>
+        <v>131334143</v>
       </c>
       <c r="B11" t="n">
-        <v>92349</v>
+        <v>57948</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493806</v>
+        <v>493853</v>
       </c>
       <c r="R11" t="n">
-        <v>6676345</v>
+        <v>6676360</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1772,7 +1774,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1782,7 +1784,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på Gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1791,72 +1798,69 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Karl Ericson, Bo karlstens, Erik Danielsson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131334143</v>
+        <v>131335070</v>
       </c>
       <c r="B12" t="n">
-        <v>57948</v>
+        <v>92352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493853</v>
+        <v>493806</v>
       </c>
       <c r="R12" t="n">
-        <v>6676360</v>
+        <v>6676345</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1885,7 +1889,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,12 +1899,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på Gran</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1909,18 +1908,19 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson, Bo karlstens, Erik Danielsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1930,7 +1930,7 @@
         <v>131333525</v>
       </c>
       <c r="B13" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>131333559</v>
       </c>
       <c r="B14" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>131333951</v>
       </c>
       <c r="B15" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2412,34 +2412,30 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131332689</v>
+        <v>131334595</v>
       </c>
       <c r="B17" t="n">
-        <v>92349</v>
+        <v>91912</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2447,13 +2443,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493701</v>
+        <v>493840</v>
       </c>
       <c r="R17" t="n">
-        <v>6676314</v>
+        <v>6676287</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2482,7 +2478,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2492,7 +2488,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2507,42 +2503,46 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131334595</v>
+        <v>131332689</v>
       </c>
       <c r="B18" t="n">
-        <v>91909</v>
+        <v>92352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2550,13 +2550,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493840</v>
+        <v>493701</v>
       </c>
       <c r="R18" t="n">
-        <v>6676287</v>
+        <v>6676314</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2610,12 +2610,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2625,7 +2625,7 @@
         <v>131333773</v>
       </c>
       <c r="B19" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2743,48 +2743,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131334166</v>
+        <v>131334199</v>
       </c>
       <c r="B20" t="n">
-        <v>92349</v>
+        <v>57945</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493800</v>
+        <v>493835</v>
       </c>
       <c r="R20" t="n">
-        <v>6676342</v>
+        <v>6676206</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2813,7 +2818,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2823,7 +2828,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Spillning på kanten, används troligen av någon.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2838,22 +2848,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131333621</v>
+        <v>131334166</v>
       </c>
       <c r="B21" t="n">
-        <v>99095</v>
+        <v>92352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2861,51 +2871,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493698</v>
+        <v>493800</v>
       </c>
       <c r="R21" t="n">
-        <v>6676232</v>
+        <v>6676342</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2934,7 +2930,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2944,7 +2940,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2959,50 +2955,59 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131334199</v>
+        <v>131333621</v>
       </c>
       <c r="B22" t="n">
-        <v>57945</v>
+        <v>99098</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3011,10 +3016,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493835</v>
+        <v>493698</v>
       </c>
       <c r="R22" t="n">
-        <v>6676206</v>
+        <v>6676232</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3046,7 +3051,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3056,12 +3061,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Spillning på kanten, används troligen av någon.</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3091,7 +3091,7 @@
         <v>131333841</v>
       </c>
       <c r="B23" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 7214-2026 artfynd.xlsx
+++ b/artfynd/A 7214-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131334014</v>
+        <v>131334034</v>
       </c>
       <c r="B2" t="n">
-        <v>93180</v>
+        <v>4775</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>100299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493766</v>
+        <v>493833</v>
       </c>
       <c r="R2" t="n">
-        <v>6676216</v>
+        <v>6676350</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,19 +775,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131334077</v>
+        <v>131334014</v>
       </c>
       <c r="B3" t="n">
         <v>93180</v>
@@ -835,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493772</v>
+        <v>493766</v>
       </c>
       <c r="R3" t="n">
-        <v>6676229</v>
+        <v>6676216</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,47 +903,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131334261</v>
+        <v>131334077</v>
       </c>
       <c r="B4" t="n">
-        <v>99098</v>
+        <v>93180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -956,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493838</v>
+        <v>493772</v>
       </c>
       <c r="R4" t="n">
-        <v>6676206</v>
+        <v>6676229</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -991,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1154,38 +1145,47 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131334034</v>
+        <v>131334261</v>
       </c>
       <c r="B6" t="n">
-        <v>4775</v>
+        <v>99098</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493833</v>
+        <v>493838</v>
       </c>
       <c r="R6" t="n">
-        <v>6676350</v>
+        <v>6676206</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,12 +1254,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 7214-2026 artfynd.xlsx
+++ b/artfynd/A 7214-2026 artfynd.xlsx
@@ -2412,44 +2412,57 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131334595</v>
+        <v>131333773</v>
       </c>
       <c r="B17" t="n">
-        <v>91912</v>
+        <v>99098</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493840</v>
+        <v>493773</v>
       </c>
       <c r="R17" t="n">
-        <v>6676287</v>
+        <v>6676285</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2478,7 +2491,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2488,7 +2501,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ant. Flera det fanns snö kvar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2503,12 +2521,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2622,57 +2640,44 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131333773</v>
+        <v>131334595</v>
       </c>
       <c r="B19" t="n">
-        <v>99098</v>
+        <v>91912</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493773</v>
+        <v>493840</v>
       </c>
       <c r="R19" t="n">
-        <v>6676285</v>
+        <v>6676287</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2701,7 +2706,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2711,12 +2716,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ant. Flera det fanns snö kvar.</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2731,65 +2731,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131334199</v>
+        <v>131334166</v>
       </c>
       <c r="B20" t="n">
-        <v>57945</v>
+        <v>92352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493835</v>
+        <v>493800</v>
       </c>
       <c r="R20" t="n">
-        <v>6676206</v>
+        <v>6676342</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2818,7 +2813,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2828,12 +2823,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Spillning på kanten, används troligen av någon.</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2848,60 +2838,65 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131334166</v>
+        <v>131334199</v>
       </c>
       <c r="B21" t="n">
-        <v>92352</v>
+        <v>57945</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493800</v>
+        <v>493835</v>
       </c>
       <c r="R21" t="n">
-        <v>6676342</v>
+        <v>6676206</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2930,7 +2925,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2940,7 +2935,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Spillning på kanten, används troligen av någon.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2955,12 +2955,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 7214-2026 artfynd.xlsx
+++ b/artfynd/A 7214-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131334034</v>
+        <v>131333681</v>
       </c>
       <c r="B2" t="n">
-        <v>4775</v>
+        <v>97435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100299</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>493833</v>
+        <v>493703</v>
       </c>
       <c r="R2" t="n">
-        <v>6676350</v>
+        <v>6676222</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,66 +770,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131334014</v>
+        <v>131333871</v>
       </c>
       <c r="B3" t="n">
-        <v>93180</v>
+        <v>97435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>493766</v>
+        <v>493751</v>
       </c>
       <c r="R3" t="n">
-        <v>6676216</v>
+        <v>6676206</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,57 +889,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131334077</v>
+        <v>131332689</v>
       </c>
       <c r="B4" t="n">
-        <v>93180</v>
+        <v>92406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>493772</v>
+        <v>493701</v>
       </c>
       <c r="R4" t="n">
-        <v>6676229</v>
+        <v>6676314</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,22 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131334158</v>
+        <v>131334166</v>
       </c>
       <c r="B5" t="n">
-        <v>58109</v>
+        <v>92406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,51 +1007,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>493840</v>
+        <v>493800</v>
       </c>
       <c r="R5" t="n">
-        <v>6676215</v>
+        <v>6676342</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1113,12 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Mellan äldre och yngre skog.</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,71 +1091,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131334261</v>
+        <v>131335070</v>
       </c>
       <c r="B6" t="n">
-        <v>99098</v>
+        <v>92406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>493838</v>
+        <v>493806</v>
       </c>
       <c r="R6" t="n">
-        <v>6676206</v>
+        <v>6676345</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1229,7 +1176,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1239,7 +1186,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,6 +1195,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1259,17 +1207,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Karl Ericson, Bo karlstens, Erik Danielsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131333871</v>
+        <v>131333951</v>
       </c>
       <c r="B7" t="n">
-        <v>97338</v>
+        <v>93271</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,34 +1225,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>493751</v>
+        <v>493761</v>
       </c>
       <c r="R7" t="n">
-        <v>6676206</v>
+        <v>6676203</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1336,7 +1293,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1346,7 +1303,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Mest troligt dropp, kanske skarp.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1373,45 +1335,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131333748</v>
+        <v>131334014</v>
       </c>
       <c r="B8" t="n">
-        <v>99098</v>
+        <v>93271</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493720</v>
+        <v>493766</v>
       </c>
       <c r="R8" t="n">
-        <v>6676196</v>
+        <v>6676216</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1443,7 +1414,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1453,7 +1424,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131335349</v>
+        <v>131334042</v>
       </c>
       <c r="B9" t="n">
-        <v>57945</v>
+        <v>93271</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,27 +1462,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1520,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493785</v>
+        <v>493772</v>
       </c>
       <c r="R9" t="n">
-        <v>6676325</v>
+        <v>6676229</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1555,7 +1530,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1565,7 +1540,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Möjligen samma mycel, större yta.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,45 +1572,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131333681</v>
+        <v>131334199</v>
       </c>
       <c r="B10" t="n">
-        <v>97338</v>
+        <v>57972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493703</v>
+        <v>493835</v>
       </c>
       <c r="R10" t="n">
-        <v>6676222</v>
+        <v>6676206</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1662,7 +1647,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1672,7 +1657,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Spillning på kanten, används troligen av någon.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1699,27 +1689,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131334143</v>
+        <v>131334642</v>
       </c>
       <c r="B11" t="n">
-        <v>57948</v>
+        <v>57972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1728,24 +1718,23 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>493853</v>
+        <v>493863</v>
       </c>
       <c r="R11" t="n">
-        <v>6676360</v>
+        <v>6676372</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1774,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1784,12 +1773,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre ringhack på Gran</t>
+          <t>Hackmärken nära mark</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1804,60 +1793,62 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131335070</v>
+        <v>131335349</v>
       </c>
       <c r="B12" t="n">
-        <v>92352</v>
+        <v>57972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493806</v>
+        <v>493785</v>
       </c>
       <c r="R12" t="n">
-        <v>6676345</v>
+        <v>6676325</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1889,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1899,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1908,7 +1899,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1920,54 +1910,45 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Karl Ericson, Bo karlstens, Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131333525</v>
+        <v>131334143</v>
       </c>
       <c r="B13" t="n">
-        <v>99098</v>
+        <v>57975</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1976,13 +1957,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493710</v>
+        <v>493853</v>
       </c>
       <c r="R13" t="n">
-        <v>6676254</v>
+        <v>6676360</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2011,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,12 +2002,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Några överblommade, runt tallstam</t>
+          <t>Äldre ringhack på Gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,59 +2022,50 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131333559</v>
+        <v>131335314</v>
       </c>
       <c r="B14" t="n">
-        <v>99098</v>
+        <v>57975</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2102,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493702</v>
+        <v>493768</v>
       </c>
       <c r="R14" t="n">
-        <v>6676254</v>
+        <v>6676338</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2137,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2147,7 +2119,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2174,10 +2151,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131333951</v>
+        <v>131334034</v>
       </c>
       <c r="B15" t="n">
-        <v>93180</v>
+        <v>4776</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2185,31 +2162,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>100299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2218,13 +2191,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>493761</v>
+        <v>493833</v>
       </c>
       <c r="R15" t="n">
-        <v>6676203</v>
+        <v>6676350</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2253,7 +2226,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2263,12 +2236,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Mest troligt dropp, kanske skarp.</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2283,50 +2251,50 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131335314</v>
+        <v>131335379</v>
       </c>
       <c r="B16" t="n">
-        <v>57948</v>
+        <v>44182</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>101735</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2335,13 +2303,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>493768</v>
+        <v>493745</v>
       </c>
       <c r="R16" t="n">
-        <v>6676338</v>
+        <v>6676360</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2370,7 +2338,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2380,12 +2348,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran.</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2400,54 +2363,59 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131333773</v>
+        <v>131334158</v>
       </c>
       <c r="B17" t="n">
-        <v>99098</v>
+        <v>58136</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2456,13 +2424,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493773</v>
+        <v>493840</v>
       </c>
       <c r="R17" t="n">
-        <v>6676285</v>
+        <v>6676215</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2491,7 +2459,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2501,12 +2469,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ant. Flera det fanns snö kvar.</t>
+          <t>Mellan äldre och yngre skog.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2521,22 +2489,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131332689</v>
+        <v>131333525</v>
       </c>
       <c r="B18" t="n">
-        <v>92352</v>
+        <v>99195</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2544,37 +2512,51 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493701</v>
+        <v>493710</v>
       </c>
       <c r="R18" t="n">
-        <v>6676314</v>
+        <v>6676254</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2603,7 +2585,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2613,7 +2595,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Några överblommade, runt tallstam</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,53 +2615,71 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131334595</v>
+        <v>131333559</v>
       </c>
       <c r="B19" t="n">
-        <v>91912</v>
+        <v>99195</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>493840</v>
+        <v>493702</v>
       </c>
       <c r="R19" t="n">
-        <v>6676287</v>
+        <v>6676254</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2706,7 +2711,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2716,7 +2721,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2743,10 +2748,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131334166</v>
+        <v>131333621</v>
       </c>
       <c r="B20" t="n">
-        <v>92352</v>
+        <v>99195</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2754,37 +2759,51 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>493800</v>
+        <v>493698</v>
       </c>
       <c r="R20" t="n">
-        <v>6676342</v>
+        <v>6676232</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2813,7 +2832,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2823,7 +2842,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2838,62 +2857,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131334199</v>
+        <v>131333748</v>
       </c>
       <c r="B21" t="n">
-        <v>57945</v>
+        <v>99195</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>493835</v>
+        <v>493720</v>
       </c>
       <c r="R21" t="n">
-        <v>6676206</v>
+        <v>6676196</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2925,7 +2939,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2935,12 +2949,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Spillning på kanten, används troligen av någon.</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2967,10 +2976,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131333621</v>
+        <v>131333773</v>
       </c>
       <c r="B22" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2997,7 +3006,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3005,24 +3014,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Sexberget, Sexberget, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>493698</v>
+        <v>493773</v>
       </c>
       <c r="R22" t="n">
-        <v>6676232</v>
+        <v>6676285</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3051,7 +3055,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3061,7 +3065,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ant. Flera det fanns snö kvar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3076,12 +3085,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens, Erik Danielsson, Karl Ericson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3091,7 +3100,7 @@
         <v>131333841</v>
       </c>
       <c r="B23" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3197,6 +3206,127 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131334261</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sexberget, Sexberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>493838</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6676206</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
